--- a/counselor_forms/043_mentor_application_form--counselor_forms.xlsx
+++ b/counselor_forms/043_mentor_application_form--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mento_form_date</t>
+          <t>mento_form_date_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mento_form_time</t>
+          <t>mento_form_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mento_form_note</t>
+          <t>mento_form_note_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mento_form_select_multiple</t>
+          <t>mento_form_select_multiple_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Mento Form Select Multiple 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mento_form_select_one</t>
+          <t>mento_form_select_one_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Mento Form Select One 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mento_form_email</t>
+          <t>mento_form_email_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emails to Repeat</t>
+          <t>Mento Form Email 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mento_form_phone</t>
+          <t>mento_form_phone_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phones to Repeat</t>
+          <t>Mento Form Phone 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mento_form_note</t>
+          <t>mento_form_note_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mentor Notes</t>
+          <t>Mento Form Note 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mento_form_date</t>
+          <t>mento_form_date_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Available Dates</t>
+          <t>Mento Form Date 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mento_form_time</t>
+          <t>mento_form_time_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Available Times</t>
+          <t>Mento Form Time 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mento_form_note</t>
+          <t>mento_form_note_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Mento Form Note 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mento_form_select_multiple_choices</t>
+          <t>mento_form_select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mento_form_select_multiple_choices</t>
+          <t>mento_form_select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mento_form_select_one_choices</t>
+          <t>mento_form_select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mento_form_select_one_choices</t>
+          <t>mento_form_select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
